--- a/Result/profitability/2609.xlsx
+++ b/Result/profitability/2609.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.23</v>
       </c>
       <c r="M2" t="n">
-        <v>2.154999999999999</v>
+        <v>1.345</v>
       </c>
       <c r="N2" t="n">
-        <v>18.65625</v>
+        <v>14.90875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.33</v>
       </c>
       <c r="M3" t="n">
-        <v>1.181249999999999</v>
+        <v>0.9374999999999996</v>
       </c>
       <c r="N3" t="n">
-        <v>13.78</v>
+        <v>12.1625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.12</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7474999999999996</v>
+        <v>0.6737499999999995</v>
       </c>
       <c r="N4" t="n">
-        <v>10.62125</v>
+        <v>10.18875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.41</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4174999999999995</v>
+        <v>0.5874999999999996</v>
       </c>
       <c r="N5" t="n">
-        <v>7.970000000000001</v>
+        <v>8.210000000000003</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-1.21</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2312499999999995</v>
+        <v>0.2199999999999995</v>
       </c>
       <c r="N6" t="n">
-        <v>4.947500000000002</v>
+        <v>5.152500000000002</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-1.5</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1725000000000004</v>
+        <v>-0.04875000000000046</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7375000000000016</v>
+        <v>2.221250000000001</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-1.47</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4375000000000004</v>
+        <v>-0.2837500000000004</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.748749999999998</v>
+        <v>-0.4687499999999984</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         <v>-0.7662500000000004</v>
       </c>
       <c r="N10" t="n">
-        <v>-4.301249999999999</v>
+        <v>-4.301249999999998</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1772,10 +1772,10 @@
         <v>1.05</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6762500000000004</v>
+        <v>-0.6762500000000005</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.381249999999998</v>
+        <v>-3.381249999999999</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1899,10 +1899,10 @@
         <v>2.99</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3175000000000003</v>
+        <v>-0.3175000000000004</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7387499999999987</v>
+        <v>-0.7387499999999978</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>-0.1975000000000004</v>
       </c>
       <c r="N13" t="n">
-        <v>1.133750000000001</v>
+        <v>1.133750000000002</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2609</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>45923</v>
+      </c>
+      <c r="D75" t="n">
+        <v>37867</v>
+      </c>
+      <c r="E75" t="n">
+        <v>8056</v>
+      </c>
+      <c r="F75" t="n">
+        <v>17.54</v>
+      </c>
+      <c r="G75" t="n">
+        <v>5684</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>12.38%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1291</v>
+      </c>
+      <c r="J75" t="n">
+        <v>6975</v>
+      </c>
+      <c r="K75" t="n">
+        <v>5734</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.331249999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>20.12875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X75" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>1.402739726027397</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>4.857142857142856</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1229193341869399</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
